--- a/output/2026-09-30_21_Malesia_Johor_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-30_21_Malesia_Johor_Utensilerie_e_Macchine_Utensili.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Verificato: azienda attiva dal 1981, marchio proprio SOUSTA, sito ufficiale coerente col settore</t>
+          <t>Verificato: azienda attiva dal 1981, marchio proprio SOUSTA, sito ufficiale coerente col settore [DUPLICATO — vedi anche: 2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -652,7 +652,6 @@
           <t>+607-236 2814</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Verificato: rivenditore di macchine utensili CNC dal 1991;  nessuna email generica reperita, lasciata vuota</t>
@@ -739,7 +738,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Verificato: fondata nel 2013, fornitore e riparatore di hardware/macchinari/power tools</t>
+          <t>Verificato: fondata nel 2013, fornitore e riparatore di hardware/macchinari/power tools [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +857,6 @@
           <t>+607-351 4117</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Verificato: distributore/importatore ufficiale di marchi power tools;  nessuna email generica reperita</t>
@@ -987,7 +985,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>TENUTO: fuori dalla categoria stretta ma fortemente affine al core business Dupuy (aspirazione industriale, depolverazione, trattamento aria);  distribuisce prodotti di terzi (non solo propri), buon potenziale partner</t>
+          <t>TENUTO: fuori dalla categoria stretta ma fortemente affine al core business Dupuy (aspirazione industriale, depolverazione, trattamento aria);  distribuisce prodotti di terzi (non solo propri), buon potenziale partner [DUPLICATO — vedi anche: 2026-09-30_17_Malesia_Johor_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1113,7 +1111,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Verificato: filiale fisica JB confermata con indirizzo dedicato, dubbio iniziale sulla sede risolto</t>
+          <t>Verificato: filiale fisica JB confermata con indirizzo dedicato, dubbio iniziale sulla sede risolto [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1232,10 +1230,9 @@
           <t>+607-238 3900</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Verificato: attiva dal 2007;  sito ora raggiungibile (precedente segnalazione HTTP 503 superata);  nessuna email generica reperita</t>
+          <t>Verificato: attiva dal 2007;  sito ora raggiungibile (precedente segnalazione HTTP 503 superata);  nessuna email generica reperita [DUPLICATO — vedi anche: 2026-09-30_19_Malesia_Johor_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">

--- a/output/2026-09-30_21_Malesia_Johor_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-30_21_Malesia_Johor_Utensilerie_e_Macchine_Utensili.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (01/10/2026)</t>
         </is>
       </c>
     </row>
